--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The type of omics experiment that the sample was subject to. This will be a proteomics-based data, by default, but this should specify the type of proteomics data.</t>
+          <t>The type of proteomics data generated. Must match experimental_strategy: Whole Cell Proteomics = Proteome, Phospho-Proteomics = Phosphoproteome, Ubiquitylomics = Ubiquitylome, Acetylomics = Acetylome, Glycoproteomics = Glycoproteome</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>"Proteome", "Ubiquitylome", "Phosphoproteome", "Acetylome", "Glycoproteome", "Metabolome", "Lipidome"</t>
+          <t>"Proteome", "Phosphoproteome", "Ubiquitylome", "Acetylome", "Glycoproteome"</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Metabolome</t>
+          <t>Phosphoproteome</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>"Whole Cell Proteomics", "Phospho-Proteomics"</t>
+          <t>"Whole Cell Proteomics", "Phospho-Proteomics", "Ubiquitylomics", "Acetylomics", "Glycoproteomics"</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Whole Cell Proteomics</t>
+          <t>Phospho-Proteomics</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1490,7 +1490,11 @@
           <t>Data acquisition type</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>"DDA", "DIA"</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1516,10 +1520,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Reporter ion MS level</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Peptide fragmentation method used for MS/MS</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>"HCD fragmentation", "CID fragmentation"</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1527,7 +1535,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>HCD fragmentation</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1545,10 +1553,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Enrichment method used for phospho, ubiquitin, acetyl, or other enrichment</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-ε-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-ε-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1556,7 +1568,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>metabolome</t>
+          <t>phosphopeptide enrichment</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1577,7 +1589,11 @@
           <t>Approach used for peptide quantification</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>"LFQ", "TMT", "SILAC"</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1585,7 +1601,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Stable isotopic labeling</t>
+          <t>TMT</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1614,7 +1630,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>L-Lysine SILAC</t>
+          <t>TMT11plex</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1690,10 +1706,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Method used to fractionate sample.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Method used to fractionate sample, or None if the sample was not fractionated</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>"HpH", "None"</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1701,7 +1721,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>reverse-phase HPLC</t>
+          <t>HpH</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1714,12 +1734,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample.</t>
+          <t>Number of fractions generated for sample; leave blank or use 1 if not fractionated</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -2206,7 +2226,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="16">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2220,7 +2240,7 @@
       <formula1>'Lists'!$D$2:$D$8</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$8</formula1>
+      <formula1>'Lists'!$E$2:$E$6</formula1>
     </dataValidation>
     <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$26</formula1>
@@ -2229,16 +2249,31 @@
       <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$3</formula1>
+      <formula1>'Lists'!$H$2:$H$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$3</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$3</formula1>
+      <formula1>'Lists'!$N$2:$N$3</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+      <formula1>'Lists'!$O$2:$O$2</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$4</formula1>
+      <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2251,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,15 +2332,40 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>acquisition_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ion_fragmentation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>enrichment_approach</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>quantification_technique</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fractionation_approach</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
@@ -2354,15 +2414,40 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>DDA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HCD fragmentation</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>whole proteome</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>LFQ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HpH</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -2391,7 +2476,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ubiquitylome</t>
+          <t>Phosphoproteome</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2411,10 +2496,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CID fragmentation</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>phosphopeptide enrichment</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2443,7 +2553,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phosphoproteome</t>
+          <t>Ubiquitylome</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2456,7 +2566,22 @@
           <t>SHA256</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ubiquitylomics</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>ubiquitin remnant (K-ε-GG) enrichment</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SILAC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
@@ -2498,6 +2623,16 @@
           <t>SHA512</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Acetylomics</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>acetyl-lysine enrichment</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2535,6 +2670,16 @@
           <t>ETag</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Glycoproteomics</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>glycopeptide enrichment</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2552,11 +2697,6 @@
           <t>sra</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Metabolome</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>GVCF</t>
@@ -2577,11 +2717,6 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>synapse</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Lipidome</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>The type of omics experiment that the sample was subject to. This will be a proteomics-based data, by default, but this should specify the type of proteomics data.</t>
+          <t>The type of proteomics data generated. Must match experimental_strategy: Whole Cell Proteomics = Proteome, Phospho-Proteomics = Phosphoproteome, Ubiquitylomics = Ubiquitylome, Acetylomics = Acetylome, Glycoproteomics = Glycoproteome</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>"Proteome", "Ubiquitylome", "Phosphoproteome", "Acetylome", "Glycoproteome", "Metabolome", "Lipidome"</t>
+          <t>"Proteome", "Phosphoproteome", "Ubiquitylome", "Acetylome", "Glycoproteome"</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Metabolome</t>
+          <t>Phosphoproteome</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "MZML", "RAW"</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>MZML</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>"Whole Cell Proteomics", "Phospho-Proteomics"</t>
+          <t>"Whole Cell Proteomics", "Phospho-Proteomics", "Ubiquitylomics", "Acetylomics", "Glycoproteomics"</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Whole Cell Proteomics</t>
+          <t>Phospho-Proteomics</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1490,7 +1490,11 @@
           <t>Data acquisition type</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>"DDA", "DIA"</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1516,10 +1520,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Reporter ion MS level</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Peptide fragmentation method used for MS/MS</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>"HCD fragmentation", "CID fragmentation"</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1527,7 +1535,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>MS2</t>
+          <t>HCD fragmentation</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1545,10 +1553,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Enrichment method used for phospho, ubiquitin, acetyl, or other enrichment</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-ε-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-ε-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1556,7 +1568,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>metabolome</t>
+          <t>phosphopeptide enrichment</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1577,7 +1589,11 @@
           <t>Approach used for peptide quantification</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>"LFQ", "TMT", "SILAC"</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1585,7 +1601,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Stable isotopic labeling</t>
+          <t>TMT</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1614,7 +1630,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>L-Lysine SILAC</t>
+          <t>TMT11plex</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1690,10 +1706,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Method used to fractionate sample.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Method used to fractionate sample, or None if the sample was not fractionated</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>"HpH", "None"</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1701,7 +1721,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>reverse-phase HPLC</t>
+          <t>HpH</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1714,12 +1734,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample.</t>
+          <t>Number of fractions generated for sample; leave blank or use 1 if not fractionated</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1738,7 +1758,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1748,30 +1768,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1781,7 +1801,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1792,7 +1812,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -1804,7 +1824,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1814,14 +1834,10 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1829,30 +1845,34 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>host_organism</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Binomial name of organism with full genus name</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>"Mus musculus"</t>
+          <t>"Homo sapiens", "Mus musculus"</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1862,50 +1882,83 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>host_organism</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>reported_gender</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>"Female", "Male", "Not Reported"</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1916,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1966,6 +2019,7 @@
     <col width="24" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2181,32 +2235,37 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="17">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2220,7 +2279,7 @@
       <formula1>'Lists'!$D$2:$D$8</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$8</formula1>
+      <formula1>'Lists'!$E$2:$E$6</formula1>
     </dataValidation>
     <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$F$2:$F$26</formula1>
@@ -2229,16 +2288,34 @@
       <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$3</formula1>
+      <formula1>'Lists'!$H$2:$H$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$3</formula1>
     </dataValidation>
+    <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$K$2:$K$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$N$2:$N$3</formula1>
+    </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$2</formula1>
+      <formula1>'Lists'!$O$2:$O$3</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$4</formula1>
+      <formula1>'Lists'!$P$2:$P$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$Q$2:$Q$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2251,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2297,15 +2374,45 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>acquisition_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ion_fragmentation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>enrichment_approach</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>quantification_technique</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fractionation_approach</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
@@ -2354,15 +2461,45 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>DDA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HCD fragmentation</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>whole proteome</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>LFQ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HpH</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -2391,7 +2528,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ubiquitylome</t>
+          <t>Phosphoproteome</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2411,10 +2548,40 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>DIA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CID fragmentation</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>phosphopeptide enrichment</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2443,7 +2610,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phosphoproteome</t>
+          <t>Ubiquitylome</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2456,7 +2623,22 @@
           <t>SHA256</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ubiquitylomics</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>ubiquitin remnant (K-ε-GG) enrichment</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SILAC</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
@@ -2498,6 +2680,16 @@
           <t>SHA512</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Acetylomics</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>acetyl-lysine enrichment</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2535,6 +2727,16 @@
           <t>ETag</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Glycoproteomics</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>glycopeptide enrichment</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2552,11 +2754,6 @@
           <t>sra</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Metabolome</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>GVCF</t>
@@ -2579,11 +2776,6 @@
           <t>synapse</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Lipidome</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>VCF</t>
@@ -2795,14 +2987,14 @@
     <row r="25">
       <c r="F25" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>MZML</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="F26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>RAW</t>
         </is>
       </c>
     </row>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -1553,12 +1553,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-ε-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
+          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-ε-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
+          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample; leave blank or use 1 if not fractionated</t>
+          <t>Number of fractions generated for sample. Required when fractionation_approach is HpH; leave blank if not fractionated</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ubiquitin remnant (K-ε-GG) enrichment</t>
+          <t>ubiquitin remnant (K-GG) enrichment</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "MZML", "RAW"</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>MZML</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-ε-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
+          <t>Enrichment method used; must match experimental_strategy: "whole proteome" for Whole Cell Proteomics, "phosphopeptide enrichment" for Phospho-Proteomics, "ubiquitin remnant (K-GG) enrichment" for Ubiquitylomics, "acetyl-lysine enrichment" for Acetylomics, "glycopeptide enrichment" for Glycoproteomics</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-ε-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
+          <t>"whole proteome", "phosphopeptide enrichment", "ubiquitin remnant (K-GG) enrichment", "acetyl-lysine enrichment", "glycopeptide enrichment"</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample; leave blank or use 1 if not fractionated</t>
+          <t>Number of fractions generated for sample. Required when fractionation_approach is HpH; leave blank if not fractionated</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1768,30 +1768,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1834,14 +1834,10 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1849,30 +1845,34 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>host_organism</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Binomial name of organism with full genus name</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>"Mus musculus"</t>
+          <t>"Homo sapiens", "Mus musculus"</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1882,50 +1882,83 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>host_organism</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>reported_gender</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>"Female", "Male", "Not Reported"</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1936,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1986,6 +2019,7 @@
     <col width="24" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2201,32 +2235,37 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="16">
+  <dataValidations count="17">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2266,14 +2305,17 @@
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$M$2:$M$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$N$2:$N$3</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$O$2:$O$2</formula1>
+      <formula1>'Lists'!$O$2:$O$3</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$4</formula1>
+      <formula1>'Lists'!$P$2:$P$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$Q$2:$Q$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2286,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,15 +2399,20 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
@@ -2439,15 +2486,20 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -2521,10 +2573,15 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2573,7 +2630,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ubiquitin remnant (K-ε-GG) enrichment</t>
+          <t>ubiquitin remnant (K-GG) enrichment</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2581,7 +2638,7 @@
           <t>SILAC</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
@@ -2930,14 +2987,14 @@
     <row r="25">
       <c r="F25" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>MZML</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="F26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>RAW</t>
         </is>
       </c>
     </row>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when composition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1918,11 +1918,7 @@
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
+          <t>Full hash value of the file</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$20</formula1>
+      <formula1>'Lists'!$C$2:$C$21</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -2953,6 +2953,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Extracellular Vesicles</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>PED</t>

--- a/excel_templates/proteomics_manifest_template.xlsx
+++ b/excel_templates/proteomics_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$21</formula1>
+      <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -2953,11 +2953,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Extracellular Vesicles</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>PED</t>
